--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2018/Airline_Cumulative_Statistics_2018.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2018/Airline_Cumulative_Statistics_2018.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="36">
   <si>
     <t>Row</t>
   </si>
@@ -25,6 +25,9 @@
   </si>
   <si>
     <t>American</t>
+  </si>
+  <si>
+    <t>Avelo</t>
   </si>
   <si>
     <t>Delta</t>
@@ -163,7 +166,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -186,40 +189,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2">
@@ -233,7 +236,7 @@
         <v>55366048892</v>
       </c>
       <c r="D2" s="0">
-        <v>668672</v>
+        <v>668107</v>
       </c>
       <c r="E2" s="0">
         <v>161</v>
@@ -245,7 +248,7 @@
         <v>3.1299999999999999</v>
       </c>
       <c r="H2" s="0">
-        <v>10.31</v>
+        <v>10.300000000000001</v>
       </c>
       <c r="I2" s="0">
         <v>84.459999999999994</v>
@@ -254,13 +257,13 @@
         <v>1306</v>
       </c>
       <c r="K2" s="0">
-        <v>4182.8900000000003</v>
+        <v>4185.21</v>
       </c>
       <c r="L2" s="0">
-        <v>25.640000000000001</v>
+        <v>25.649999999999999</v>
       </c>
       <c r="M2" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="3">
@@ -268,40 +271,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>10148166202</v>
+        <v>12385035233</v>
       </c>
       <c r="C3" s="0">
-        <v>11980894416</v>
+        <v>14580892158</v>
       </c>
       <c r="D3" s="0">
-        <v>478661</v>
+        <v>437865</v>
       </c>
       <c r="E3" s="0">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F3" s="0">
-        <v>79523</v>
+        <v>97173</v>
       </c>
       <c r="G3" s="0">
-        <v>3.1800000000000002</v>
+        <v>2.9199999999999999</v>
       </c>
       <c r="H3" s="0">
-        <v>7.3399999999999999</v>
+        <v>6.7300000000000004</v>
       </c>
       <c r="I3" s="0">
-        <v>84.700000000000003</v>
+        <v>84.939999999999998</v>
       </c>
       <c r="J3" s="0">
         <v>885</v>
       </c>
       <c r="K3" s="0">
-        <v>3849.1999999999998</v>
+        <v>4086.1700000000001</v>
       </c>
       <c r="L3" s="0">
-        <v>22.600000000000001</v>
+        <v>24.100000000000001</v>
       </c>
       <c r="M3" s="0">
-        <v>0.058999999999999997</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="4">
@@ -309,40 +312,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>201248248741</v>
+        <v>205418392664</v>
       </c>
       <c r="C4" s="0">
-        <v>243468196062</v>
+        <v>248527733789</v>
       </c>
       <c r="D4" s="0">
-        <v>749894</v>
+        <v>734702</v>
       </c>
       <c r="E4" s="0">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F4" s="0">
-        <v>1042751</v>
+        <v>1097579</v>
       </c>
       <c r="G4" s="0">
-        <v>3.21</v>
+        <v>3.2400000000000002</v>
       </c>
       <c r="H4" s="0">
-        <v>10.390000000000001</v>
+        <v>10.300000000000001</v>
       </c>
       <c r="I4" s="0">
-        <v>82.659999999999997</v>
+        <v>82.650000000000006</v>
       </c>
       <c r="J4" s="0">
-        <v>1267</v>
+        <v>1236</v>
       </c>
       <c r="K4" s="0">
-        <v>5513.8599999999997</v>
+        <v>5471.8599999999997</v>
       </c>
       <c r="L4" s="0">
-        <v>30.809999999999999</v>
+        <v>30.789999999999999</v>
       </c>
       <c r="M4" s="0">
-        <v>0.075999999999999998</v>
+        <v>0.076999999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -350,40 +353,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>185641711960</v>
+        <v>78103877</v>
       </c>
       <c r="C5" s="0">
-        <v>215159749364</v>
+        <v>145117104</v>
       </c>
       <c r="D5" s="0">
-        <v>835183</v>
+        <v>0</v>
       </c>
       <c r="E5" s="0">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F5" s="0">
-        <v>831930</v>
+        <v>1530</v>
       </c>
       <c r="G5" s="0">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="H5" s="0">
-        <v>10.65</v>
+        <v>0</v>
       </c>
       <c r="I5" s="0">
-        <v>86.280000000000001</v>
+        <v>53.82</v>
       </c>
       <c r="J5" s="0">
-        <v>1342</v>
+        <v>565</v>
       </c>
       <c r="K5" s="0">
-        <v>5140.6999999999998</v>
+        <v>0</v>
       </c>
       <c r="L5" s="0">
-        <v>27.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="M5" s="0">
-        <v>0.066000000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -391,40 +394,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>20875202333</v>
+        <v>204440703449</v>
       </c>
       <c r="C6" s="0">
-        <v>24443949064</v>
+        <v>237417060353</v>
       </c>
       <c r="D6" s="0">
-        <v>838845</v>
+        <v>758158</v>
       </c>
       <c r="E6" s="0">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="F6" s="0">
-        <v>122441</v>
+        <v>1100877</v>
       </c>
       <c r="G6" s="0">
-        <v>4.2000000000000002</v>
+        <v>3.52</v>
       </c>
       <c r="H6" s="0">
-        <v>11.69</v>
+        <v>10.23</v>
       </c>
       <c r="I6" s="0">
-        <v>85.400000000000006</v>
+        <v>86.109999999999999</v>
       </c>
       <c r="J6" s="0">
-        <v>1052</v>
+        <v>1147</v>
       </c>
       <c r="K6" s="0">
-        <v>4008.27</v>
+        <v>5036.3999999999996</v>
       </c>
       <c r="L6" s="0">
-        <v>21.120000000000001</v>
+        <v>27.719999999999999</v>
       </c>
       <c r="M6" s="0">
-        <v>0.056000000000000001</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="7">
@@ -432,40 +435,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>17190233073</v>
+        <v>20875202333</v>
       </c>
       <c r="C7" s="0">
-        <v>20147017075</v>
+        <v>24443949064</v>
       </c>
       <c r="D7" s="0">
-        <v>979913</v>
+        <v>838845</v>
       </c>
       <c r="E7" s="0">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="F7" s="0">
-        <v>89705</v>
+        <v>122441</v>
       </c>
       <c r="G7" s="0">
-        <v>4.3600000000000003</v>
+        <v>4.2000000000000002</v>
       </c>
       <c r="H7" s="0">
-        <v>9.9199999999999999</v>
+        <v>11.69</v>
       </c>
       <c r="I7" s="0">
-        <v>85.319999999999993</v>
+        <v>85.400000000000006</v>
       </c>
       <c r="J7" s="0">
-        <v>901</v>
+        <v>1052</v>
       </c>
       <c r="K7" s="0">
-        <v>6740.0799999999999</v>
+        <v>4008.27</v>
       </c>
       <c r="L7" s="0">
-        <v>29.079999999999998</v>
+        <v>21.120000000000001</v>
       </c>
       <c r="M7" s="0">
-        <v>0.068000000000000005</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -473,40 +476,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>50819592338</v>
+        <v>17190233073</v>
       </c>
       <c r="C8" s="0">
-        <v>60409181191</v>
+        <v>20147017075</v>
       </c>
       <c r="D8" s="0">
-        <v>670468</v>
+        <v>979913</v>
       </c>
       <c r="E8" s="0">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="F8" s="0">
-        <v>367443</v>
+        <v>89705</v>
       </c>
       <c r="G8" s="0">
-        <v>4.0800000000000001</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="H8" s="0">
-        <v>11.76</v>
+        <v>9.9199999999999999</v>
       </c>
       <c r="I8" s="0">
-        <v>84.129999999999995</v>
+        <v>85.319999999999993</v>
       </c>
       <c r="J8" s="0">
-        <v>1093</v>
+        <v>901</v>
       </c>
       <c r="K8" s="0">
-        <v>3951.98</v>
+        <v>6740.0799999999999</v>
       </c>
       <c r="L8" s="0">
-        <v>26.739999999999998</v>
+        <v>29.079999999999998</v>
       </c>
       <c r="M8" s="0">
-        <v>0.069000000000000006</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="9">
@@ -514,40 +517,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>133371040685</v>
+        <v>50819592338</v>
       </c>
       <c r="C9" s="0">
-        <v>159850173477</v>
+        <v>60409181191</v>
       </c>
       <c r="D9" s="0">
-        <v>604029</v>
+        <v>670468</v>
       </c>
       <c r="E9" s="0">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="F9" s="0">
-        <v>1375426</v>
+        <v>367443</v>
       </c>
       <c r="G9" s="0">
-        <v>5.2000000000000002</v>
+        <v>4.0800000000000001</v>
       </c>
       <c r="H9" s="0">
-        <v>10.619999999999999</v>
+        <v>11.76</v>
       </c>
       <c r="I9" s="0">
-        <v>83.439999999999998</v>
+        <v>84.129999999999995</v>
       </c>
       <c r="J9" s="0">
-        <v>757</v>
+        <v>1093</v>
       </c>
       <c r="K9" s="0">
-        <v>3731.79</v>
+        <v>3951.98</v>
       </c>
       <c r="L9" s="0">
-        <v>24.420000000000002</v>
+        <v>26.739999999999998</v>
       </c>
       <c r="M9" s="0">
-        <v>0.066000000000000003</v>
+        <v>0.069000000000000006</v>
       </c>
     </row>
     <row r="10">
@@ -555,40 +558,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>30591799219</v>
+        <v>133371040685</v>
       </c>
       <c r="C10" s="0">
-        <v>36270040450</v>
+        <v>159850173477</v>
       </c>
       <c r="D10" s="0">
-        <v>835330</v>
+        <v>604029</v>
       </c>
       <c r="E10" s="0">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="F10" s="0">
-        <v>191168</v>
+        <v>1375426</v>
       </c>
       <c r="G10" s="0">
-        <v>4.4000000000000004</v>
+        <v>5.2000000000000002</v>
       </c>
       <c r="H10" s="0">
-        <v>12.01</v>
+        <v>10.619999999999999</v>
       </c>
       <c r="I10" s="0">
-        <v>84.340000000000003</v>
+        <v>83.439999999999998</v>
       </c>
       <c r="J10" s="0">
-        <v>1038</v>
+        <v>757</v>
       </c>
       <c r="K10" s="0">
-        <v>3553.0300000000002</v>
+        <v>3731.79</v>
       </c>
       <c r="L10" s="0">
-        <v>19.440000000000001</v>
+        <v>24.420000000000002</v>
       </c>
       <c r="M10" s="0">
-        <v>0.050999999999999997</v>
+        <v>0.066000000000000003</v>
       </c>
     </row>
     <row r="11">
@@ -596,40 +599,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>4189014201</v>
+        <v>30591799219</v>
       </c>
       <c r="C11" s="0">
-        <v>5254202646</v>
+        <v>36270040450</v>
       </c>
       <c r="D11" s="0">
-        <v>569870</v>
+        <v>835330</v>
       </c>
       <c r="E11" s="0">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="F11" s="0">
-        <v>24181</v>
+        <v>191168</v>
       </c>
       <c r="G11" s="0">
-        <v>2.6200000000000001</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H11" s="0">
-        <v>8.6199999999999992</v>
+        <v>12.01</v>
       </c>
       <c r="I11" s="0">
-        <v>79.730000000000004</v>
+        <v>84.340000000000003</v>
       </c>
       <c r="J11" s="0">
-        <v>1317</v>
+        <v>1038</v>
       </c>
       <c r="K11" s="0">
-        <v>4159.5200000000004</v>
+        <v>3553.0300000000002</v>
       </c>
       <c r="L11" s="0">
-        <v>25.219999999999999</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="M11" s="0">
-        <v>0.063</v>
+        <v>0.050999999999999997</v>
       </c>
     </row>
     <row r="12">
@@ -637,40 +640,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>204781794621</v>
+        <v>4189014201</v>
       </c>
       <c r="C12" s="0">
-        <v>244575401125</v>
+        <v>5254202646</v>
       </c>
       <c r="D12" s="0">
-        <v>0</v>
+        <v>569870</v>
       </c>
       <c r="E12" s="0">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F12" s="0">
-        <v>785007</v>
+        <v>24181</v>
       </c>
       <c r="G12" s="0">
-        <v>0</v>
+        <v>2.6200000000000001</v>
       </c>
       <c r="H12" s="0">
-        <v>0</v>
+        <v>8.6199999999999992</v>
       </c>
       <c r="I12" s="0">
-        <v>83.730000000000004</v>
+        <v>79.730000000000004</v>
       </c>
       <c r="J12" s="0">
-        <v>1584</v>
+        <v>1317</v>
       </c>
       <c r="K12" s="0">
-        <v>5549.2200000000003</v>
+        <v>4159.5200000000004</v>
       </c>
       <c r="L12" s="0">
-        <v>29.07</v>
+        <v>25.219999999999999</v>
       </c>
       <c r="M12" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="13">
@@ -678,19 +681,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>657197554</v>
+        <v>204781794621</v>
       </c>
       <c r="C13" s="0">
-        <v>797824350</v>
+        <v>244575401125</v>
       </c>
       <c r="D13" s="0">
         <v>0</v>
       </c>
       <c r="E13" s="0">
-        <v>50</v>
+        <v>172</v>
       </c>
       <c r="F13" s="0">
-        <v>46317</v>
+        <v>785007</v>
       </c>
       <c r="G13" s="0">
         <v>0</v>
@@ -699,19 +702,19 @@
         <v>0</v>
       </c>
       <c r="I13" s="0">
-        <v>82.370000000000005</v>
+        <v>83.730000000000004</v>
       </c>
       <c r="J13" s="0">
-        <v>345</v>
+        <v>1584</v>
       </c>
       <c r="K13" s="0">
-        <v>0</v>
+        <v>5549.2200000000003</v>
       </c>
       <c r="L13" s="0">
-        <v>0</v>
+        <v>29.07</v>
       </c>
       <c r="M13" s="0">
-        <v>0</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="14">
@@ -719,40 +722,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>6851175353</v>
+        <v>657841266</v>
       </c>
       <c r="C14" s="0">
-        <v>8634045026</v>
+        <v>798707910</v>
       </c>
       <c r="D14" s="0">
-        <v>154510</v>
+        <v>0</v>
       </c>
       <c r="E14" s="0">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="F14" s="0">
-        <v>255652</v>
+        <v>46443</v>
       </c>
       <c r="G14" s="0">
-        <v>4.5800000000000001</v>
+        <v>0</v>
       </c>
       <c r="H14" s="0">
-        <v>7.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="I14" s="0">
-        <v>79.349999999999994</v>
+        <v>82.359999999999999</v>
       </c>
       <c r="J14" s="0">
-        <v>476</v>
+        <v>344</v>
       </c>
       <c r="K14" s="0">
-        <v>1119.51</v>
+        <v>0</v>
       </c>
       <c r="L14" s="0">
-        <v>16.030000000000001</v>
+        <v>0</v>
       </c>
       <c r="M14" s="0">
-        <v>0.058000000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -760,40 +763,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>5562182260</v>
+        <v>6851175353</v>
       </c>
       <c r="C15" s="0">
-        <v>7099454699</v>
+        <v>8634045026</v>
       </c>
       <c r="D15" s="0">
-        <v>80147</v>
+        <v>154510</v>
       </c>
       <c r="E15" s="0">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F15" s="0">
-        <v>234243</v>
+        <v>255652</v>
       </c>
       <c r="G15" s="0">
-        <v>2.6400000000000001</v>
+        <v>4.5800000000000001</v>
       </c>
       <c r="H15" s="0">
-        <v>4.46</v>
+        <v>7.9500000000000002</v>
       </c>
       <c r="I15" s="0">
-        <v>78.349999999999994</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="J15" s="0">
         <v>476</v>
       </c>
       <c r="K15" s="0">
-        <v>1403.27</v>
+        <v>1119.51</v>
       </c>
       <c r="L15" s="0">
-        <v>22.43</v>
+        <v>16.030000000000001</v>
       </c>
       <c r="M15" s="0">
-        <v>0.078</v>
+        <v>0.058000000000000003</v>
       </c>
     </row>
     <row r="16">
@@ -801,40 +804,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>2799588299</v>
+        <v>6501584098</v>
       </c>
       <c r="C16" s="0">
-        <v>3417316854</v>
+        <v>8327623231</v>
       </c>
       <c r="D16" s="0">
-        <v>173468</v>
+        <v>67077</v>
       </c>
       <c r="E16" s="0">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F16" s="0">
-        <v>92970</v>
+        <v>312381</v>
       </c>
       <c r="G16" s="0">
-        <v>4.7199999999999998</v>
+        <v>2.52</v>
       </c>
       <c r="H16" s="0">
-        <v>8.2300000000000004</v>
+        <v>4.1299999999999999</v>
       </c>
       <c r="I16" s="0">
-        <v>81.920000000000002</v>
+        <v>78.069999999999993</v>
       </c>
       <c r="J16" s="0">
-        <v>519</v>
+        <v>446</v>
       </c>
       <c r="K16" s="0">
-        <v>1076.8800000000001</v>
+        <v>1395.21</v>
       </c>
       <c r="L16" s="0">
-        <v>15.210000000000001</v>
+        <v>23.93</v>
       </c>
       <c r="M16" s="0">
-        <v>0.050999999999999997</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
     <row r="17">
@@ -842,40 +845,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>1055649396</v>
+        <v>2799588299</v>
       </c>
       <c r="C17" s="0">
-        <v>1288641392</v>
+        <v>3417316854</v>
       </c>
       <c r="D17" s="0">
-        <v>245924</v>
+        <v>173468</v>
       </c>
       <c r="E17" s="0">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F17" s="0">
-        <v>26765</v>
+        <v>92970</v>
       </c>
       <c r="G17" s="0">
-        <v>5.1100000000000003</v>
+        <v>4.7199999999999998</v>
       </c>
       <c r="H17" s="0">
-        <v>9.7899999999999991</v>
+        <v>8.2300000000000004</v>
       </c>
       <c r="I17" s="0">
         <v>81.920000000000002</v>
       </c>
       <c r="J17" s="0">
-        <v>633</v>
+        <v>519</v>
       </c>
       <c r="K17" s="0">
-        <v>773.53999999999996</v>
+        <v>1076.8800000000001</v>
       </c>
       <c r="L17" s="0">
-        <v>10.17</v>
+        <v>15.210000000000001</v>
       </c>
       <c r="M17" s="0">
-        <v>0.031</v>
+        <v>0.050999999999999997</v>
       </c>
     </row>
     <row r="18">
@@ -883,40 +886,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>8251766479</v>
+        <v>2592682715</v>
       </c>
       <c r="C18" s="0">
-        <v>10128037729</v>
+        <v>3271781972</v>
       </c>
       <c r="D18" s="0">
-        <v>225068</v>
+        <v>153605</v>
       </c>
       <c r="E18" s="0">
         <v>76</v>
       </c>
       <c r="F18" s="0">
-        <v>234365</v>
+        <v>123145</v>
       </c>
       <c r="G18" s="0">
-        <v>5.21</v>
+        <v>5.7800000000000002</v>
       </c>
       <c r="H18" s="0">
-        <v>9.5099999999999998</v>
+        <v>7.8899999999999997</v>
       </c>
       <c r="I18" s="0">
-        <v>81.469999999999999</v>
+        <v>79.239999999999995</v>
       </c>
       <c r="J18" s="0">
-        <v>568</v>
+        <v>350</v>
       </c>
       <c r="K18" s="0">
-        <v>1020.25</v>
+        <v>1476.1600000000001</v>
       </c>
       <c r="L18" s="0">
-        <v>13.42</v>
+        <v>19.420000000000002</v>
       </c>
       <c r="M18" s="0">
-        <v>0.042999999999999997</v>
+        <v>0.075999999999999998</v>
       </c>
     </row>
     <row r="19">
@@ -924,40 +927,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>977973736</v>
+        <v>8251766479</v>
       </c>
       <c r="C19" s="0">
-        <v>1258952194</v>
+        <v>10128037729</v>
       </c>
       <c r="D19" s="0">
-        <v>0</v>
+        <v>225068</v>
       </c>
       <c r="E19" s="0">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="F19" s="0">
-        <v>90937</v>
+        <v>234365</v>
       </c>
       <c r="G19" s="0">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="H19" s="0">
-        <v>0</v>
+        <v>9.5099999999999998</v>
       </c>
       <c r="I19" s="0">
-        <v>77.680000000000007</v>
+        <v>81.469999999999999</v>
       </c>
       <c r="J19" s="0">
-        <v>277</v>
+        <v>568</v>
       </c>
       <c r="K19" s="0">
-        <v>0</v>
+        <v>1020.25</v>
       </c>
       <c r="L19" s="0">
-        <v>0</v>
+        <v>13.42</v>
       </c>
       <c r="M19" s="0">
-        <v>0</v>
+        <v>0.042999999999999997</v>
       </c>
     </row>
     <row r="20">
@@ -965,40 +968,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>5292012095</v>
+        <v>1026254478</v>
       </c>
       <c r="C20" s="0">
-        <v>6907404356</v>
+        <v>1324294916</v>
       </c>
       <c r="D20" s="0">
-        <v>145388</v>
+        <v>0</v>
       </c>
       <c r="E20" s="0">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="F20" s="0">
-        <v>270077</v>
+        <v>98789</v>
       </c>
       <c r="G20" s="0">
-        <v>5.6799999999999997</v>
+        <v>0</v>
       </c>
       <c r="H20" s="0">
-        <v>8.5600000000000005</v>
+        <v>0</v>
       </c>
       <c r="I20" s="0">
-        <v>76.609999999999999</v>
+        <v>77.489999999999995</v>
       </c>
       <c r="J20" s="0">
-        <v>386</v>
+        <v>269</v>
       </c>
       <c r="K20" s="0">
-        <v>1354.6099999999999</v>
+        <v>0</v>
       </c>
       <c r="L20" s="0">
-        <v>20.48</v>
+        <v>0</v>
       </c>
       <c r="M20" s="0">
-        <v>0.080000000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1006,40 +1009,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>11158068235</v>
+        <v>5292012095</v>
       </c>
       <c r="C21" s="0">
-        <v>14157584805</v>
+        <v>6907404356</v>
       </c>
       <c r="D21" s="0">
-        <v>205540</v>
+        <v>145388</v>
       </c>
       <c r="E21" s="0">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F21" s="0">
-        <v>324089</v>
+        <v>270077</v>
       </c>
       <c r="G21" s="0">
-        <v>4.71</v>
+        <v>5.6799999999999997</v>
       </c>
       <c r="H21" s="0">
-        <v>9.3699999999999992</v>
+        <v>8.5600000000000005</v>
       </c>
       <c r="I21" s="0">
-        <v>78.810000000000002</v>
+        <v>76.609999999999999</v>
       </c>
       <c r="J21" s="0">
-        <v>591</v>
+        <v>386</v>
       </c>
       <c r="K21" s="0">
-        <v>1406.6600000000001</v>
+        <v>1354.6099999999999</v>
       </c>
       <c r="L21" s="0">
-        <v>19.030000000000001</v>
+        <v>20.48</v>
       </c>
       <c r="M21" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.080000000000000002</v>
       </c>
     </row>
     <row r="22">
@@ -1047,40 +1050,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>20769916267</v>
+        <v>11158068235</v>
       </c>
       <c r="C22" s="0">
-        <v>25793730803</v>
+        <v>14157584805</v>
       </c>
       <c r="D22" s="0">
-        <v>173836</v>
+        <v>205540</v>
       </c>
       <c r="E22" s="0">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="F22" s="0">
-        <v>798261</v>
+        <v>324089</v>
       </c>
       <c r="G22" s="0">
-        <v>5.3799999999999999</v>
+        <v>4.71</v>
       </c>
       <c r="H22" s="0">
-        <v>9.3800000000000008</v>
+        <v>9.3699999999999992</v>
       </c>
       <c r="I22" s="0">
-        <v>80.519999999999996</v>
+        <v>78.810000000000002</v>
       </c>
       <c r="J22" s="0">
-        <v>492</v>
+        <v>591</v>
       </c>
       <c r="K22" s="0">
-        <v>1309.0699999999999</v>
+        <v>1406.6600000000001</v>
       </c>
       <c r="L22" s="0">
-        <v>20.34</v>
+        <v>19.030000000000001</v>
       </c>
       <c r="M22" s="0">
-        <v>0.070999999999999994</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1088,40 +1091,81 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>968994985638</v>
+        <v>20769916267</v>
       </c>
       <c r="C23" s="0">
-        <v>1156407845970</v>
+        <v>25793730803</v>
       </c>
       <c r="D23" s="0">
-        <v>0</v>
+        <v>173836</v>
       </c>
       <c r="E23" s="0">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="F23" s="0">
-        <v>7542544</v>
+        <v>798261</v>
       </c>
       <c r="G23" s="0">
-        <v>0</v>
+        <v>5.3799999999999999</v>
       </c>
       <c r="H23" s="0">
-        <v>0</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="I23" s="0">
-        <v>83.790000000000006</v>
+        <v>80.519999999999996</v>
       </c>
       <c r="J23" s="0">
-        <v>946</v>
+        <v>492</v>
       </c>
       <c r="K23" s="0">
-        <v>4051.6100000000001</v>
+        <v>1309.0699999999999</v>
       </c>
       <c r="L23" s="0">
-        <v>26.57</v>
+        <v>20.34</v>
       </c>
       <c r="M23" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.070999999999999994</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="0">
+        <v>996804453569</v>
+      </c>
+      <c r="C24" s="0">
+        <v>1189747344926</v>
+      </c>
+      <c r="D24" s="0">
+        <v>0</v>
+      </c>
+      <c r="E24" s="0">
+        <v>131</v>
+      </c>
+      <c r="F24" s="0">
+        <v>8067995</v>
+      </c>
+      <c r="G24" s="0">
+        <v>0</v>
+      </c>
+      <c r="H24" s="0">
+        <v>0</v>
+      </c>
+      <c r="I24" s="0">
+        <v>83.780000000000001</v>
+      </c>
+      <c r="J24" s="0">
+        <v>916</v>
+      </c>
+      <c r="K24" s="0">
+        <v>4031.71</v>
+      </c>
+      <c r="L24" s="0">
+        <v>26.640000000000001</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.068000000000000005</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2018/Airline_Cumulative_Statistics_2018.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2018/Airline_Cumulative_Statistics_2018.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="40">
   <si>
     <t>Row</t>
   </si>
@@ -82,6 +82,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -166,7 +178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -189,40 +201,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2">
@@ -687,7 +699,7 @@
         <v>244575401125</v>
       </c>
       <c r="D13" s="0">
-        <v>0</v>
+        <v>884668</v>
       </c>
       <c r="E13" s="0">
         <v>172</v>
@@ -696,10 +708,10 @@
         <v>785007</v>
       </c>
       <c r="G13" s="0">
-        <v>0</v>
+        <v>2.8399999999999999</v>
       </c>
       <c r="H13" s="0">
-        <v>0</v>
+        <v>10.720000000000001</v>
       </c>
       <c r="I13" s="0">
         <v>83.730000000000004</v>
@@ -1132,39 +1144,203 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
+        <v>614640890734</v>
+      </c>
+      <c r="C24" s="0">
+        <v>730520195267</v>
+      </c>
+      <c r="D24" s="0">
+        <v>787300</v>
+      </c>
+      <c r="E24" s="0">
+        <v>166</v>
+      </c>
+      <c r="F24" s="0">
+        <v>2983463</v>
+      </c>
+      <c r="G24" s="0">
+        <v>3.2200000000000002</v>
+      </c>
+      <c r="H24" s="0">
+        <v>10.4</v>
+      </c>
+      <c r="I24" s="0">
+        <v>84.140000000000001</v>
+      </c>
+      <c r="J24" s="0">
+        <v>1295</v>
+      </c>
+      <c r="K24" s="0">
+        <v>5351.0299999999997</v>
+      </c>
+      <c r="L24" s="0">
+        <v>29.23</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.070999999999999994</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>248143518687</v>
+      </c>
+      <c r="C25" s="0">
+        <v>295772420635</v>
+      </c>
+      <c r="D25" s="0">
+        <v>645552</v>
+      </c>
+      <c r="E25" s="0">
+        <v>151</v>
+      </c>
+      <c r="F25" s="0">
+        <v>2091867</v>
+      </c>
+      <c r="G25" s="0">
+        <v>4.5700000000000003</v>
+      </c>
+      <c r="H25" s="0">
+        <v>10.76</v>
+      </c>
+      <c r="I25" s="0">
+        <v>83.900000000000006</v>
+      </c>
+      <c r="J25" s="0">
+        <v>890</v>
+      </c>
+      <c r="K25" s="0">
+        <v>3982.1999999999998</v>
+      </c>
+      <c r="L25" s="0">
+        <v>25.399999999999999</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.066000000000000003</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>68119154863</v>
+      </c>
+      <c r="C26" s="0">
+        <v>80694201422</v>
+      </c>
+      <c r="D26" s="0">
+        <v>701201</v>
+      </c>
+      <c r="E26" s="0">
+        <v>180</v>
+      </c>
+      <c r="F26" s="0">
+        <v>436493</v>
+      </c>
+      <c r="G26" s="0">
+        <v>3.79</v>
+      </c>
+      <c r="H26" s="0">
+        <v>10.15</v>
+      </c>
+      <c r="I26" s="0">
+        <v>84.420000000000002</v>
+      </c>
+      <c r="J26" s="0">
+        <v>1022</v>
+      </c>
+      <c r="K26" s="0">
+        <v>3820.79</v>
+      </c>
+      <c r="L26" s="0">
+        <v>21.100000000000001</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>65900889285</v>
+      </c>
+      <c r="C27" s="0">
+        <v>82760527602</v>
+      </c>
+      <c r="D27" s="0">
+        <v>155917</v>
+      </c>
+      <c r="E27" s="0">
+        <v>66</v>
+      </c>
+      <c r="F27" s="0">
+        <v>2556172</v>
+      </c>
+      <c r="G27" s="0">
+        <v>4.8200000000000003</v>
+      </c>
+      <c r="H27" s="0">
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="I27" s="0">
+        <v>79.629999999999995</v>
+      </c>
+      <c r="J27" s="0">
+        <v>476</v>
+      </c>
+      <c r="K27" s="0">
+        <v>1226.4100000000001</v>
+      </c>
+      <c r="L27" s="0">
+        <v>18.32</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.065000000000000002</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
         <v>996804453569</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C28" s="0">
         <v>1189747344926</v>
       </c>
-      <c r="D24" s="0">
-        <v>0</v>
-      </c>
-      <c r="E24" s="0">
+      <c r="D28" s="0">
+        <v>585526</v>
+      </c>
+      <c r="E28" s="0">
         <v>131</v>
       </c>
-      <c r="F24" s="0">
+      <c r="F28" s="0">
         <v>8067995</v>
       </c>
-      <c r="G24" s="0">
-        <v>0</v>
-      </c>
-      <c r="H24" s="0">
-        <v>0</v>
-      </c>
-      <c r="I24" s="0">
+      <c r="G28" s="0">
+        <v>3.9700000000000002</v>
+      </c>
+      <c r="H28" s="0">
+        <v>9.9000000000000004</v>
+      </c>
+      <c r="I28" s="0">
         <v>83.780000000000001</v>
       </c>
-      <c r="J24" s="0">
+      <c r="J28" s="0">
         <v>916</v>
       </c>
-      <c r="K24" s="0">
+      <c r="K28" s="0">
         <v>4031.71</v>
       </c>
-      <c r="L24" s="0">
+      <c r="L28" s="0">
         <v>26.640000000000001</v>
       </c>
-      <c r="M24" s="0">
+      <c r="M28" s="0">
         <v>0.068000000000000005</v>
       </c>
     </row>
